--- a/outputs/382-29.xlsx
+++ b/outputs/382-29.xlsx
@@ -498,95 +498,95 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -594,15 +594,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,7 +610,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -618,23 +618,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8151,7 +8151,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="35" t="n">
-        <f aca="false">'Employee 1'!AB5+'Employee 2'!AB5+'Employee 3'!AB5</f>
+        <f aca="false">+'Employee 1'!AB5+'Employee 2'!AB5+'Employee 3'!AB5</f>
         <v>42</v>
       </c>
     </row>
@@ -8160,7 +8160,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="35" t="n">
-        <f aca="false">'Employee 1'!AB6+'Employee 2'!AB6+'Employee 3'!AB6</f>
+        <f aca="false">+'Employee 1'!AB6+'Employee 2'!AB6+'Employee 3'!AB6</f>
         <v>36</v>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="35" t="n">
-        <f aca="false">'Employee 1'!AB7+'Employee 2'!AB7+'Employee 3'!AB7</f>
+        <f aca="false">+'Employee 1'!AB7+'Employee 2'!AB7+'Employee 3'!AB7</f>
         <v>18</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="35" t="n">
-        <f aca="false">'Employee 1'!AB8+'Employee 2'!AB8+'Employee 3'!AB8</f>
+        <f aca="false">+'Employee 1'!AB8+'Employee 2'!AB8+'Employee 3'!AB8</f>
         <v>12</v>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="35" t="n">
-        <f aca="false">'Employee 1'!AB9+'Employee 2'!AB9+'Employee 3'!AB9</f>
+        <f aca="false">+'Employee 1'!AB9+'Employee 2'!AB9+'Employee 3'!AB9</f>
         <v>60</v>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="35" t="n">
-        <f aca="false">'Employee 1'!AB10+'Employee 2'!AB10+'Employee 3'!AB10</f>
+        <f aca="false">+'Employee 1'!AB10+'Employee 2'!AB10+'Employee 3'!AB10</f>
         <v>48</v>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="35" t="n">
-        <f aca="false">'Employee 1'!AB11+'Employee 2'!AB11+'Employee 3'!AB11</f>
+        <f aca="false">+'Employee 1'!AB11+'Employee 2'!AB11+'Employee 3'!AB11</f>
         <v>0</v>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="35" t="n">
-        <f aca="false">'Employee 1'!AB12+'Employee 2'!AB12+'Employee 3'!AB12</f>
+        <f aca="false">+'Employee 1'!AB12+'Employee 2'!AB12+'Employee 3'!AB12</f>
         <v>42</v>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="35" t="n">
-        <f aca="false">'Employee 1'!AB13+'Employee 2'!AB13+'Employee 3'!AB13</f>
+        <f aca="false">+'Employee 1'!AB13+'Employee 2'!AB13+'Employee 3'!AB13</f>
         <v>3</v>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="35" t="n">
-        <f aca="false">'Employee 1'!AB14+'Employee 2'!AB14+'Employee 3'!AB14</f>
+        <f aca="false">+'Employee 1'!AB14+'Employee 2'!AB14+'Employee 3'!AB14</f>
         <v>6</v>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="35" t="n">
-        <f aca="false">'Employee 1'!AB15+'Employee 2'!AB15+'Employee 3'!AB15</f>
+        <f aca="false">+'Employee 1'!AB15+'Employee 2'!AB15+'Employee 3'!AB15</f>
         <v>54</v>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="35" t="n">
-        <f aca="false">'Employee 1'!AB16+'Employee 2'!AB16+'Employee 3'!AB16</f>
+        <f aca="false">+'Employee 1'!AB16+'Employee 2'!AB16+'Employee 3'!AB16</f>
         <v>30</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="35" t="n">
-        <f aca="false">'Employee 1'!AB17+'Employee 2'!AB17+'Employee 3'!AB17</f>
+        <f aca="false">+'Employee 1'!AB17+'Employee 2'!AB17+'Employee 3'!AB17</f>
         <v>39</v>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="35" t="n">
-        <f aca="false">'Employee 1'!AB18+'Employee 2'!AB18+'Employee 3'!AB18</f>
+        <f aca="false">+'Employee 1'!AB18+'Employee 2'!AB18+'Employee 3'!AB18</f>
         <v>60</v>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="35" t="n">
-        <f aca="false">'Employee 1'!AB19+'Employee 2'!AB19+'Employee 3'!AB19</f>
+        <f aca="false">+'Employee 1'!AB19+'Employee 2'!AB19+'Employee 3'!AB19</f>
         <v>36</v>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="35" t="n">
-        <f aca="false">'Employee 1'!AB20+'Employee 2'!AB20+'Employee 3'!AB20</f>
+        <f aca="false">+'Employee 1'!AB20+'Employee 2'!AB20+'Employee 3'!AB20</f>
         <v>30</v>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="35" t="n">
-        <f aca="false">'Employee 1'!AB21+'Employee 2'!AB21+'Employee 3'!AB21</f>
+        <f aca="false">+'Employee 1'!AB21+'Employee 2'!AB21+'Employee 3'!AB21</f>
         <v>15</v>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="35" t="n">
-        <f aca="false">'Employee 1'!AB22+'Employee 2'!AB22+'Employee 3'!AB22</f>
+        <f aca="false">+'Employee 1'!AB22+'Employee 2'!AB22+'Employee 3'!AB22</f>
         <v>24</v>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="35" t="n">
-        <f aca="false">'Employee 1'!AB23+'Employee 2'!AB23+'Employee 3'!AB23</f>
+        <f aca="false">+'Employee 1'!AB23+'Employee 2'!AB23+'Employee 3'!AB23</f>
         <v>0</v>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="35" t="n">
-        <f aca="false">'Employee 1'!AB24+'Employee 2'!AB24+'Employee 3'!AB24</f>
+        <f aca="false">+'Employee 1'!AB24+'Employee 2'!AB24+'Employee 3'!AB24</f>
         <v>0</v>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="35" t="n">
-        <f aca="false">'Employee 1'!AB25+'Employee 2'!AB25+'Employee 3'!AB25</f>
+        <f aca="false">+'Employee 1'!AB25+'Employee 2'!AB25+'Employee 3'!AB25</f>
         <v>39</v>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="35" t="n">
-        <f aca="false">'Employee 1'!AB26+'Employee 2'!AB26+'Employee 3'!AB26</f>
+        <f aca="false">+'Employee 1'!AB26+'Employee 2'!AB26+'Employee 3'!AB26</f>
         <v>66</v>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="35" t="n">
-        <f aca="false">'Employee 1'!AB27+'Employee 2'!AB27+'Employee 3'!AB27</f>
+        <f aca="false">+'Employee 1'!AB27+'Employee 2'!AB27+'Employee 3'!AB27</f>
         <v>45</v>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="35" t="n">
-        <f aca="false">'Employee 1'!AB28+'Employee 2'!AB28+'Employee 3'!AB28</f>
+        <f aca="false">+'Employee 1'!AB28+'Employee 2'!AB28+'Employee 3'!AB28</f>
         <v>15</v>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="35" t="n">
-        <f aca="false">'Employee 1'!AB29+'Employee 2'!AB29+'Employee 3'!AB29</f>
+        <f aca="false">+'Employee 1'!AB29+'Employee 2'!AB29+'Employee 3'!AB29</f>
         <v>69</v>
       </c>
     </row>

--- a/outputs/382-29.xlsx
+++ b/outputs/382-29.xlsx
@@ -8151,7 +8151,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB5+'Employee 2'!AB5+'Employee 3'!AB5</f>
+        <f aca="false">+'Employee 1'!AB5++'Employee 2'!AB5++'Employee 3'!AB5</f>
         <v>42</v>
       </c>
     </row>
@@ -8160,7 +8160,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB6+'Employee 2'!AB6+'Employee 3'!AB6</f>
+        <f aca="false">+'Employee 1'!AB6++'Employee 2'!AB6++'Employee 3'!AB6</f>
         <v>36</v>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB7+'Employee 2'!AB7+'Employee 3'!AB7</f>
+        <f aca="false">+'Employee 1'!AB7++'Employee 2'!AB7++'Employee 3'!AB7</f>
         <v>18</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB8+'Employee 2'!AB8+'Employee 3'!AB8</f>
+        <f aca="false">+'Employee 1'!AB8++'Employee 2'!AB8++'Employee 3'!AB8</f>
         <v>12</v>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB9+'Employee 2'!AB9+'Employee 3'!AB9</f>
+        <f aca="false">+'Employee 1'!AB9++'Employee 2'!AB9++'Employee 3'!AB9</f>
         <v>60</v>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB10+'Employee 2'!AB10+'Employee 3'!AB10</f>
+        <f aca="false">+'Employee 1'!AB10++'Employee 2'!AB10++'Employee 3'!AB10</f>
         <v>48</v>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB11+'Employee 2'!AB11+'Employee 3'!AB11</f>
+        <f aca="false">+'Employee 1'!AB11++'Employee 2'!AB11++'Employee 3'!AB11</f>
         <v>0</v>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB12+'Employee 2'!AB12+'Employee 3'!AB12</f>
+        <f aca="false">+'Employee 1'!AB12++'Employee 2'!AB12++'Employee 3'!AB12</f>
         <v>42</v>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB13+'Employee 2'!AB13+'Employee 3'!AB13</f>
+        <f aca="false">+'Employee 1'!AB13++'Employee 2'!AB13++'Employee 3'!AB13</f>
         <v>3</v>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB14+'Employee 2'!AB14+'Employee 3'!AB14</f>
+        <f aca="false">+'Employee 1'!AB14++'Employee 2'!AB14++'Employee 3'!AB14</f>
         <v>6</v>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB15+'Employee 2'!AB15+'Employee 3'!AB15</f>
+        <f aca="false">+'Employee 1'!AB15++'Employee 2'!AB15++'Employee 3'!AB15</f>
         <v>54</v>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB16+'Employee 2'!AB16+'Employee 3'!AB16</f>
+        <f aca="false">+'Employee 1'!AB16++'Employee 2'!AB16++'Employee 3'!AB16</f>
         <v>30</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB17+'Employee 2'!AB17+'Employee 3'!AB17</f>
+        <f aca="false">+'Employee 1'!AB17++'Employee 2'!AB17++'Employee 3'!AB17</f>
         <v>39</v>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB18+'Employee 2'!AB18+'Employee 3'!AB18</f>
+        <f aca="false">+'Employee 1'!AB18++'Employee 2'!AB18++'Employee 3'!AB18</f>
         <v>60</v>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB19+'Employee 2'!AB19+'Employee 3'!AB19</f>
+        <f aca="false">+'Employee 1'!AB19++'Employee 2'!AB19++'Employee 3'!AB19</f>
         <v>36</v>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB20+'Employee 2'!AB20+'Employee 3'!AB20</f>
+        <f aca="false">+'Employee 1'!AB20++'Employee 2'!AB20++'Employee 3'!AB20</f>
         <v>30</v>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB21+'Employee 2'!AB21+'Employee 3'!AB21</f>
+        <f aca="false">+'Employee 1'!AB21++'Employee 2'!AB21++'Employee 3'!AB21</f>
         <v>15</v>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB22+'Employee 2'!AB22+'Employee 3'!AB22</f>
+        <f aca="false">+'Employee 1'!AB22++'Employee 2'!AB22++'Employee 3'!AB22</f>
         <v>24</v>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB23+'Employee 2'!AB23+'Employee 3'!AB23</f>
+        <f aca="false">+'Employee 1'!AB23++'Employee 2'!AB23++'Employee 3'!AB23</f>
         <v>0</v>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB24+'Employee 2'!AB24+'Employee 3'!AB24</f>
+        <f aca="false">+'Employee 1'!AB24++'Employee 2'!AB24++'Employee 3'!AB24</f>
         <v>0</v>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB25+'Employee 2'!AB25+'Employee 3'!AB25</f>
+        <f aca="false">+'Employee 1'!AB25++'Employee 2'!AB25++'Employee 3'!AB25</f>
         <v>39</v>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB26+'Employee 2'!AB26+'Employee 3'!AB26</f>
+        <f aca="false">+'Employee 1'!AB26++'Employee 2'!AB26++'Employee 3'!AB26</f>
         <v>66</v>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB27+'Employee 2'!AB27+'Employee 3'!AB27</f>
+        <f aca="false">+'Employee 1'!AB27++'Employee 2'!AB27++'Employee 3'!AB27</f>
         <v>45</v>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB28+'Employee 2'!AB28+'Employee 3'!AB28</f>
+        <f aca="false">+'Employee 1'!AB28++'Employee 2'!AB28++'Employee 3'!AB28</f>
         <v>15</v>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="35" t="n">
-        <f aca="false">+'Employee 1'!AB29+'Employee 2'!AB29+'Employee 3'!AB29</f>
+        <f aca="false">+'Employee 1'!AB29++'Employee 2'!AB29++'Employee 3'!AB29</f>
         <v>69</v>
       </c>
     </row>
